--- a/Mau_cau_hinh_hoc_phi1.xlsx
+++ b/Mau_cau_hinh_hoc_phi1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\tuyensinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CC50348-59B9-431D-A488-977094096FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C085012-3C29-46BF-BA54-74C5EFD4274D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -559,8 +559,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E92"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.125" bestFit="1" customWidth="1"/>
@@ -568,7 +568,7 @@
     <col min="4" max="4" width="34.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>6340113</v>
       </c>
@@ -598,8 +598,11 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5340113</v>
       </c>
@@ -612,8 +615,11 @@
       <c r="D3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4340114</v>
       </c>
@@ -626,8 +632,11 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>6340302</v>
       </c>
@@ -640,8 +649,11 @@
       <c r="D5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5340302</v>
       </c>
@@ -654,8 +666,11 @@
       <c r="D6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4340303</v>
       </c>
@@ -668,8 +683,11 @@
       <c r="D7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6340439</v>
       </c>
@@ -682,8 +700,11 @@
       <c r="D8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5340439</v>
       </c>
@@ -696,8 +717,11 @@
       <c r="D9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6340444</v>
       </c>
@@ -710,8 +734,11 @@
       <c r="D10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>5340444</v>
       </c>
@@ -724,8 +751,11 @@
       <c r="D11" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>6480102</v>
       </c>
@@ -738,8 +768,11 @@
       <c r="D12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5480102</v>
       </c>
@@ -752,8 +785,11 @@
       <c r="D13" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>6480202</v>
       </c>
@@ -766,8 +802,11 @@
       <c r="D14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>5480202</v>
       </c>
@@ -780,8 +819,11 @@
       <c r="D15" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>6510216</v>
       </c>
@@ -794,8 +836,11 @@
       <c r="D16" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>5510216</v>
       </c>
@@ -808,8 +853,11 @@
       <c r="D17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>4510217</v>
       </c>
@@ -822,8 +870,11 @@
       <c r="D18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6510305</v>
       </c>
@@ -836,8 +887,11 @@
       <c r="D19" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>5510305</v>
       </c>
@@ -850,8 +904,11 @@
       <c r="D20" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>6520123</v>
       </c>
@@ -864,8 +921,11 @@
       <c r="D21" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>5520123</v>
       </c>
@@ -878,8 +938,11 @@
       <c r="D22" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>4520123</v>
       </c>
@@ -892,8 +955,11 @@
       <c r="D23" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6520131</v>
       </c>
@@ -906,8 +972,11 @@
       <c r="D24" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>5520131</v>
       </c>
@@ -920,8 +989,11 @@
       <c r="D25" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>4520132</v>
       </c>
@@ -934,8 +1006,11 @@
       <c r="D26" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E26">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>6520205</v>
       </c>
@@ -948,8 +1023,11 @@
       <c r="D27" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5520205</v>
       </c>
@@ -962,8 +1040,11 @@
       <c r="D28" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E28">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4520206</v>
       </c>
@@ -976,8 +1057,11 @@
       <c r="D29" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E29">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>6520226</v>
       </c>
@@ -990,8 +1074,11 @@
       <c r="D30" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E30">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>5520226</v>
       </c>
@@ -1004,8 +1091,11 @@
       <c r="D31" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E31">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>4520227</v>
       </c>
@@ -1018,8 +1108,11 @@
       <c r="D32" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E32">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>6520227</v>
       </c>
@@ -1032,8 +1125,11 @@
       <c r="D33" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E33">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5520227</v>
       </c>
@@ -1046,8 +1142,11 @@
       <c r="D34" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E34">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>4520228</v>
       </c>
@@ -1060,8 +1159,11 @@
       <c r="D35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E35">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>6520228</v>
       </c>
@@ -1074,8 +1176,11 @@
       <c r="D36" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5520228</v>
       </c>
@@ -1088,8 +1193,11 @@
       <c r="D37" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E37">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>4520229</v>
       </c>
@@ -1102,8 +1210,11 @@
       <c r="D38" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E38">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6840101</v>
       </c>
@@ -1116,8 +1227,11 @@
       <c r="D39" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E39">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>5840103</v>
       </c>
@@ -1130,8 +1244,11 @@
       <c r="D40" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E40">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>6840109</v>
       </c>
@@ -1144,8 +1261,11 @@
       <c r="D41" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E41">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5840109</v>
       </c>
@@ -1158,8 +1278,11 @@
       <c r="D42" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E42">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>4840109</v>
       </c>
@@ -1172,8 +1295,11 @@
       <c r="D43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E43">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>6840110</v>
       </c>
@@ -1186,8 +1312,11 @@
       <c r="D44" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E44">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>5840110</v>
       </c>
@@ -1200,8 +1329,11 @@
       <c r="D45" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E45">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>4840110</v>
       </c>
@@ -1214,8 +1346,11 @@
       <c r="D46" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E46">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>6840111</v>
       </c>
@@ -1228,8 +1363,11 @@
       <c r="D47" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E47">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>5840111</v>
       </c>
@@ -1242,8 +1380,11 @@
       <c r="D48" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E48">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>4840111</v>
       </c>
@@ -1256,8 +1397,11 @@
       <c r="D49" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E49">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>6340113</v>
       </c>
@@ -1270,8 +1414,11 @@
       <c r="D50" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E50">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5340113</v>
       </c>
@@ -1284,8 +1431,11 @@
       <c r="D51" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E51">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6340302</v>
       </c>
@@ -1298,8 +1448,11 @@
       <c r="D52" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E52">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>5340302</v>
       </c>
@@ -1312,8 +1465,11 @@
       <c r="D53" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E53">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>5480205</v>
       </c>
@@ -1326,8 +1482,11 @@
       <c r="D54" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E54">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>6480209</v>
       </c>
@@ -1340,8 +1499,11 @@
       <c r="D55" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E55">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>5480209</v>
       </c>
@@ -1354,8 +1516,11 @@
       <c r="D56" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E56">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>6510109</v>
       </c>
@@ -1368,8 +1533,11 @@
       <c r="D57" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E57">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>5510109</v>
       </c>
@@ -1382,8 +1550,11 @@
       <c r="D58" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E58">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>4510109</v>
       </c>
@@ -1396,8 +1567,11 @@
       <c r="D59" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E59">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>6510216</v>
       </c>
@@ -1410,8 +1584,11 @@
       <c r="D60" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E60">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>5510216</v>
       </c>
@@ -1424,8 +1601,11 @@
       <c r="D61" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E61">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>6520123</v>
       </c>
@@ -1438,8 +1618,11 @@
       <c r="D62" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E62">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>5520123</v>
       </c>
@@ -1452,8 +1635,11 @@
       <c r="D63" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E63">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>4520123</v>
       </c>
@@ -1466,8 +1652,11 @@
       <c r="D64" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E64">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>6520131</v>
       </c>
@@ -1480,8 +1669,11 @@
       <c r="D65" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E65">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>5520131</v>
       </c>
@@ -1494,8 +1686,11 @@
       <c r="D66" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E66">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>6520225</v>
       </c>
@@ -1508,8 +1703,11 @@
       <c r="D67" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E67">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>5520225</v>
       </c>
@@ -1522,8 +1720,11 @@
       <c r="D68" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E68">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>5520226</v>
       </c>
@@ -1536,8 +1737,11 @@
       <c r="D69" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E69">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>6520227</v>
       </c>
@@ -1550,8 +1754,11 @@
       <c r="D70" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E70">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>5520227</v>
       </c>
@@ -1564,8 +1771,11 @@
       <c r="D71" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E71">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>6580205</v>
       </c>
@@ -1578,8 +1788,11 @@
       <c r="D72" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E72">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>5580205</v>
       </c>
@@ -1592,8 +1805,11 @@
       <c r="D73" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E73">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>4580205</v>
       </c>
@@ -1606,8 +1822,11 @@
       <c r="D74" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E74">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>5840104</v>
       </c>
@@ -1620,8 +1839,11 @@
       <c r="D75" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E75">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>6840108</v>
       </c>
@@ -1634,8 +1856,11 @@
       <c r="D76" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E76">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>5840108</v>
       </c>
@@ -1648,8 +1873,11 @@
       <c r="D77" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E77">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>4840108</v>
       </c>
@@ -1662,8 +1890,11 @@
       <c r="D78" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E78">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>6840109</v>
       </c>
@@ -1676,8 +1907,11 @@
       <c r="D79" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E79">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>5840109</v>
       </c>
@@ -1690,8 +1924,11 @@
       <c r="D80" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E80">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>4840109</v>
       </c>
@@ -1704,8 +1941,11 @@
       <c r="D81" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E81">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>5840111</v>
       </c>
@@ -1718,8 +1958,11 @@
       <c r="D82" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E82">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>4840111</v>
       </c>
@@ -1732,8 +1975,11 @@
       <c r="D83" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E83">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>3240111</v>
       </c>
@@ -1746,8 +1992,11 @@
       <c r="D84" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E84">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2840111</v>
       </c>
@@ -1760,8 +2009,11 @@
       <c r="D85" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E85">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>5340432</v>
       </c>
@@ -1774,8 +2026,11 @@
       <c r="D86" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E86">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>4340432</v>
       </c>
@@ -1788,8 +2043,11 @@
       <c r="D87" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E87">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>6480102</v>
       </c>
@@ -1802,8 +2060,11 @@
       <c r="D88" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E88">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>5480102</v>
       </c>
@@ -1816,8 +2077,11 @@
       <c r="D89" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E89">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>5510912</v>
       </c>
@@ -1830,8 +2094,11 @@
       <c r="D90" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E90">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>4510912</v>
       </c>
@@ -1844,8 +2111,11 @@
       <c r="D91" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E91">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>4850102</v>
       </c>
@@ -1858,8 +2128,10 @@
       <c r="D92" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25"/>
+      <c r="E92">
+        <v>600000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -1871,9 +2143,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1884,7 +2156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1895,7 +2167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1906,7 +2178,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1917,7 +2189,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1928,7 +2200,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
